--- a/inst/CPions_TP_formula.xlsx
+++ b/inst/CPions_TP_formula.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R_projects\CPxplorer_test\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R_projects\CPxplorer_opencode\inst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9970A86-DABC-4BA5-895D-355B51E9775C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5810CD73-D99D-45EC-B5E5-A2DDFDA689D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="3048" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TPs" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>Name of TP</t>
   </si>
@@ -36,9 +36,6 @@
     <t>General formula</t>
   </si>
   <si>
-    <t>Example formula</t>
-  </si>
-  <si>
     <t>Example adduct ion</t>
   </si>
   <si>
@@ -1159,9 +1156,6 @@
     <t>Note</t>
   </si>
   <si>
-    <t>Give exact same chemical formula as -H+OH with one less Cl</t>
-  </si>
-  <si>
     <t>Double Cl-hydroxylation</t>
   </si>
   <si>
@@ -1172,6 +1166,15 @@
   </si>
   <si>
     <t>Give exact same chemical formula as -Cl+OH with one more Cl</t>
+  </si>
+  <si>
+    <t>Example parent formula</t>
+  </si>
+  <si>
+    <t>Example molecule formula</t>
+  </si>
+  <si>
+    <t>Give exact same chemical formula as -H+OH with one less Cl (here, C10H17Cl5)</t>
   </si>
 </sst>
 </file>
@@ -1226,22 +1229,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1524,215 +1520,243 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="47.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="35.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="53.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="59.88671875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="8" width="59.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3">
+        <v>344.93104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3">
+        <v>326.9649</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3">
+        <v>360.92950000000002</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="3">
+        <v>308.99880000000002</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="5" t="s">
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="5">
-        <v>344.93104</v>
+      <c r="G6" s="3">
+        <v>376.92086999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="5">
-        <v>326.9649</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>36</v>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="3">
+        <v>358.91030000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="5">
-        <v>360.92950000000002</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>40</v>
+    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="3">
+        <v>440.88276999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5">
-        <v>308.99880000000002</v>
+    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="3">
+        <v>537.96587</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="5">
-        <v>376.92086999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5">
-        <v>358.91030000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="5">
-        <v>440.88276999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5">
-        <v>537.96587</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
